--- a/processing_scripts/DOC/tmp_doc_2022/T4 TMP Data Sheet.xlsx
+++ b/processing_scripts/DOC/tmp_doc_2022/T4 TMP Data Sheet.xlsx
@@ -36,9 +36,15 @@
     <t>Personnel:</t>
   </si>
   <si>
+    <t>AES</t>
+  </si>
+  <si>
     <t>EP</t>
   </si>
   <si>
+    <t>MKB</t>
+  </si>
+  <si>
     <t>Depth: 15cm</t>
   </si>
   <si>
@@ -96,6 +102,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Total Vol</t>
+  </si>
+  <si>
     <t>Total volume</t>
   </si>
   <si>
@@ -105,12 +114,21 @@
     <t xml:space="preserve">CONTROL </t>
   </si>
   <si>
+    <t>FRESHWATER</t>
+  </si>
+  <si>
     <t>C3</t>
   </si>
   <si>
     <t>—</t>
   </si>
   <si>
+    <t>Total Volume</t>
+  </si>
+  <si>
+    <t>SEAWATER</t>
+  </si>
+  <si>
     <t>C6</t>
   </si>
   <si>
@@ -136,24 +154,6 @@
   </si>
   <si>
     <t>I5</t>
-  </si>
-  <si>
-    <t>AES</t>
-  </si>
-  <si>
-    <t>Total Vol</t>
-  </si>
-  <si>
-    <t>FRESHWATER</t>
-  </si>
-  <si>
-    <t>MKB</t>
-  </si>
-  <si>
-    <t>Total Volume</t>
-  </si>
-  <si>
-    <t>SEAWATER</t>
   </si>
 </sst>
 </file>
@@ -161,9 +161,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="h&quot;:&quot;mm"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="M/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="h&quot;:&quot;mm"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -183,12 +183,12 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font/>
   </fonts>
   <fills count="11">
     <fill>
@@ -201,6 +201,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00DA63"/>
         <bgColor rgb="FF00DA63"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
     <fill>
@@ -229,6 +235,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
@@ -237,18 +249,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor theme="5"/>
       </patternFill>
     </fill>
   </fills>
@@ -346,30 +346,43 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="3" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
@@ -380,11 +393,8 @@
     <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -394,6 +404,9 @@
     <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -406,14 +419,23 @@
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -425,49 +447,27 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -506,11 +506,11 @@
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
+    <tableStyle count="2" pivot="0" name="SEAWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="SEAWATER-style">
+    <tableStyle count="2" pivot="0" name="FRESHWATER-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -535,7 +535,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D8:N17" displayName="Table_1" name="Table_1" id="3">
   <tableColumns count="11">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -574,7 +574,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C8:N17" displayName="Table_3" name="Table_3" id="1">
   <tableColumns count="12">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -834,19 +834,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="6">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="8">
         <v>0.5</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="G3" s="2"/>
@@ -862,8 +862,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>7</v>
+      <c r="B4" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -879,8 +879,8 @@
       <c r="N4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
+      <c r="A5" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -897,494 +897,494 @@
       <c r="N5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="12"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="27" t="s">
+      <c r="L7" s="32" t="s">
         <v>28</v>
       </c>
+      <c r="M7" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="31">
+      <c r="A8" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="38">
         <v>0.0</v>
       </c>
-      <c r="N8" s="31" t="s">
-        <v>31</v>
+      <c r="N8" s="38" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="33" t="s">
+      <c r="A9" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="35">
+      <c r="B9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="44">
         <v>0.0</v>
       </c>
-      <c r="N9" s="35" t="s">
-        <v>31</v>
+      <c r="N9" s="44" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="31" t="s">
+      <c r="A10" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="31" t="s">
-        <v>31</v>
+      <c r="N10" s="38" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="34">
+      <c r="A11" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="42">
         <v>10.0</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="35">
+      <c r="D11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="44">
         <v>1.5</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="34">
+      <c r="F11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="42">
         <v>12.5</v>
       </c>
-      <c r="J11" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="35">
+      <c r="J11" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="44">
         <v>24.0</v>
       </c>
-      <c r="N11" s="35">
+      <c r="N11" s="44">
         <v>50.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="30">
+      <c r="A12" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="31">
+      <c r="D12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="30">
+      <c r="F12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" s="31">
+      <c r="J12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="38">
         <v>40.0</v>
       </c>
-      <c r="N12" s="31">
+      <c r="N12" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="35">
+      <c r="A13" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="44">
         <v>0.0</v>
       </c>
-      <c r="N13" s="35" t="s">
-        <v>31</v>
+      <c r="N13" s="44" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="30">
+      <c r="A14" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="31">
+      <c r="D14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="30">
+      <c r="F14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="31">
+      <c r="J14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="38">
         <v>42.0</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="34">
+      <c r="A15" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="42">
         <v>7.0</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="35">
+      <c r="D15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="44">
         <v>1.5</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="36">
+      <c r="F15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="47">
         <v>1.5</v>
       </c>
-      <c r="J15" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M15" s="37">
+      <c r="J15" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="48">
         <v>11.0</v>
       </c>
-      <c r="N15" s="35" t="s">
-        <v>31</v>
+      <c r="N15" s="44" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="30">
+      <c r="A16" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="31">
+      <c r="D16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="30">
+      <c r="F16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="37">
         <v>17.5</v>
       </c>
-      <c r="J16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" s="31">
+      <c r="J16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="40"/>
+      <c r="L16" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="38">
         <v>29.0</v>
       </c>
-      <c r="N16" s="31">
+      <c r="N16" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="34">
+      <c r="A17" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="42">
         <v>10.0</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="35">
+      <c r="D17" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="44">
         <v>1.5</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="34">
+      <c r="F17" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="42">
         <v>25.0</v>
       </c>
-      <c r="J17" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" s="35">
+      <c r="J17" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="40"/>
+      <c r="L17" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="44">
         <v>42.0</v>
       </c>
-      <c r="N17" s="35">
+      <c r="N17" s="44">
         <v>48.0</v>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="38"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1528,19 +1528,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="7">
         <v>0.5111111111111111</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="7">
         <v>0.5666666666666667</v>
       </c>
       <c r="G3" s="2"/>
@@ -1555,8 +1555,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>41</v>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1571,8 +1571,8 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
+      <c r="A5" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1586,511 +1586,511 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="41"/>
+      <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="12"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="K7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="36">
+        <v>10.0</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="37">
+        <v>25.0</v>
+      </c>
+      <c r="J8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N8" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="42">
+        <v>16.0</v>
+      </c>
+      <c r="J9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="44">
+        <v>27.5</v>
+      </c>
+      <c r="N9" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="36">
+        <v>10.0</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="37">
+        <v>25.0</v>
+      </c>
+      <c r="J10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N10" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="42">
+        <v>25.0</v>
+      </c>
+      <c r="J11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N11" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="36">
+        <v>10.0</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="37">
+        <v>25.0</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M12" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N12" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="N7" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="s">
+      <c r="C13" s="43">
+        <v>10.0</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="44">
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="42">
+        <v>25.0</v>
+      </c>
+      <c r="J13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M13" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N13" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="44">
+      <c r="C14" s="36">
         <v>10.0</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="31">
+      <c r="D14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="30">
+      <c r="F14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="31">
+      <c r="J14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M14" s="38">
         <v>36.5</v>
       </c>
-      <c r="N8" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="45">
+      <c r="N14" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="43">
         <v>10.0</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="35">
+      <c r="D15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="44">
         <v>1.5</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="34">
-        <v>16.0</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="35">
-        <v>27.5</v>
-      </c>
-      <c r="N9" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="29" t="s">
+      <c r="F15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="42">
+        <v>25.0</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M15" s="38">
+        <v>36.5</v>
+      </c>
+      <c r="N15" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="44">
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="36">
         <v>10.0</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="31">
+      <c r="D16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="30">
+      <c r="F16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="31">
+      <c r="J16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M16" s="38">
         <v>36.5</v>
       </c>
-      <c r="N10" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="45">
+      <c r="N16" s="38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="43">
         <v>10.0</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="35">
+      <c r="D17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="44">
         <v>1.5</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="34">
+      <c r="F17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="42">
         <v>25.0</v>
       </c>
-      <c r="J11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="31">
+      <c r="J17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="M17" s="38">
         <v>36.5</v>
       </c>
-      <c r="N11" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="44">
-        <v>10.0</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="30">
-        <v>25.0</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M12" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N12" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="34">
-        <v>25.0</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N13" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="44">
-        <v>10.0</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="30">
-        <v>25.0</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N14" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="34">
-        <v>25.0</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M15" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N15" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="44">
-        <v>10.0</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="30">
-        <v>25.0</v>
-      </c>
-      <c r="J16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M16" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N16" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="45">
-        <v>10.0</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="34">
-        <v>25.0</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="M17" s="31">
-        <v>36.5</v>
-      </c>
-      <c r="N17" s="31" t="s">
-        <v>31</v>
+      <c r="N17" s="38" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="38"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -2170,19 +2170,19 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="39">
+      <c r="B3" s="5">
         <v>44736.0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="7">
         <v>0.5104166666666666</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="7">
         <v>0.58125</v>
       </c>
       <c r="G3" s="2"/>
@@ -2197,8 +2197,8 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>44</v>
+      <c r="B4" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2213,8 +2213,8 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
+      <c r="A5" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -2228,507 +2228,507 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="41"/>
+      <c r="N5" s="11"/>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="18" t="s">
+      <c r="G6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="12"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="K6" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="16"/>
     </row>
     <row r="7">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="22" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="E7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="G7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="H7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="I7" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="J7" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="N7" s="27" t="s">
+      <c r="K7" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="31" t="s">
         <v>28</v>
       </c>
+      <c r="M7" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="30">
+      <c r="A8" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="37">
         <v>10.0</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="31">
+      <c r="D8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="38">
         <v>1.5</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="30">
+      <c r="F8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="37">
         <v>25.0</v>
       </c>
-      <c r="J8" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="48">
+      <c r="J8" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="45">
         <v>0.5111111111111111</v>
       </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31">
+      <c r="L8" s="38"/>
+      <c r="M8" s="38">
         <f>58+56+23</f>
         <v>137</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="30">
+      <c r="A9" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="37">
         <v>10.0</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="31">
+      <c r="D9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="38">
         <v>1.5</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="30">
+      <c r="F9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="37">
         <v>25.0</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="49">
+      <c r="J9" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="46">
         <v>0.51875</v>
       </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35">
+      <c r="L9" s="44"/>
+      <c r="M9" s="44">
         <f>50+52+32</f>
         <v>134</v>
       </c>
-      <c r="N9" s="35">
+      <c r="N9" s="44">
         <v>47.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="30">
+      <c r="A10" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="37">
         <v>10.0</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="31">
+      <c r="D10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="38">
         <v>1.5</v>
       </c>
-      <c r="F10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="30">
+      <c r="F10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="37">
         <v>25.0</v>
       </c>
-      <c r="J10" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="48">
+      <c r="J10" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="45">
         <v>0.5277777777777778</v>
       </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31">
+      <c r="L10" s="38"/>
+      <c r="M10" s="38">
         <f>56+19</f>
         <v>75</v>
       </c>
-      <c r="N10" s="31">
+      <c r="N10" s="38">
         <v>47.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="30">
+      <c r="A11" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="37">
         <v>10.0</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="31">
+      <c r="D11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="38">
         <v>1.5</v>
       </c>
-      <c r="F11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="30">
+      <c r="F11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="37">
         <v>25.0</v>
       </c>
-      <c r="J11" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="49">
+      <c r="J11" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="46">
         <v>0.5340277777777778</v>
       </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35">
+      <c r="L11" s="44"/>
+      <c r="M11" s="44">
         <f>53+52</f>
         <v>105</v>
       </c>
-      <c r="N11" s="35">
+      <c r="N11" s="44">
         <v>48.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="30">
+      <c r="A12" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="37">
         <v>10.0</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="31">
+      <c r="D12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="38">
         <v>1.5</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="30">
+      <c r="F12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="37">
         <v>25.0</v>
       </c>
-      <c r="J12" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="48">
+      <c r="J12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="45">
         <v>0.5416666666666666</v>
       </c>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31">
+      <c r="L12" s="38"/>
+      <c r="M12" s="38">
         <f>59+50+1</f>
         <v>110</v>
       </c>
-      <c r="N12" s="31">
+      <c r="N12" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="30">
+      <c r="A13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="37">
         <v>10.0</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="31">
+      <c r="D13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="38">
         <v>1.5</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="30">
+      <c r="F13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="37">
         <v>25.0</v>
       </c>
-      <c r="J13" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="49">
+      <c r="J13" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="46">
         <v>0.5486111111111112</v>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="50">
+      <c r="L13" s="44"/>
+      <c r="M13" s="49">
         <f>53+55+20</f>
         <v>128</v>
       </c>
-      <c r="N13" s="35">
+      <c r="N13" s="44">
         <v>50.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="29" t="s">
+      <c r="A14" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="30">
+      <c r="B14" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="37">
         <v>10.0</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="31">
+      <c r="D14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="38">
         <v>1.5</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="30">
+      <c r="F14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="37">
         <v>25.0</v>
       </c>
-      <c r="J14" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="48">
+      <c r="J14" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="45">
         <v>0.5555555555555556</v>
       </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31">
+      <c r="L14" s="38"/>
+      <c r="M14" s="38">
         <f>55+51</f>
         <v>106</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="38">
         <v>47.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="30">
+      <c r="A15" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="37">
         <v>10.0</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="31">
+      <c r="D15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="38">
         <v>1.5</v>
       </c>
-      <c r="F15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="30">
+      <c r="F15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="37">
         <v>25.0</v>
       </c>
-      <c r="J15" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" s="49">
+      <c r="J15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="46">
         <v>0.5625</v>
       </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35">
+      <c r="L15" s="44"/>
+      <c r="M15" s="44">
         <f>56+52+14</f>
         <v>122</v>
       </c>
-      <c r="N15" s="35">
+      <c r="N15" s="44">
         <v>49.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="30">
+      <c r="A16" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="37">
         <v>10.0</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="31">
+      <c r="D16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="38">
         <v>1.5</v>
       </c>
-      <c r="F16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="30">
+      <c r="F16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="37">
         <v>25.0</v>
       </c>
-      <c r="J16" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" s="48">
+      <c r="J16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="45">
         <v>0.5694444444444444</v>
       </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31">
+      <c r="L16" s="38"/>
+      <c r="M16" s="38">
         <f>55+37</f>
         <v>92</v>
       </c>
-      <c r="N16" s="31">
+      <c r="N16" s="38">
         <v>50.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="30">
+      <c r="C17" s="37">
         <v>10.0</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="31">
+      <c r="D17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="38">
         <v>1.5</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="30">
+      <c r="F17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="37">
         <v>25.0</v>
       </c>
-      <c r="J17" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K17" s="49">
+      <c r="J17" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="46">
         <v>0.5770833333333333</v>
       </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="35">
+      <c r="L17" s="44"/>
+      <c r="M17" s="44">
         <f>56+41+30</f>
         <v>127</v>
       </c>
-      <c r="N17" s="35">
+      <c r="N17" s="44">
         <v>46.0</v>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="38"/>
+      <c r="J18" s="50"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
